--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/automation_opportunities.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/automation_opportunities.xlsx
@@ -483,11 +483,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -543,11 +543,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -623,11 +623,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
